--- a/output/df_primary.xlsx
+++ b/output/df_primary.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.703(0.603–0.804)</t>
+          <t>0.703(0.602 – 0.804)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1799,20 +1799,20 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.703(0.603–0.804)</t>
+          <t>0.703(0.602 – 0.804)</t>
         </is>
       </c>
       <c r="AQ7">
         <v>0.703</v>
       </c>
       <c r="AR7">
-        <v>0.603</v>
+        <v>0.602</v>
       </c>
       <c r="AS7">
         <v>0.804</v>
       </c>
       <c r="AT7">
-        <v>0.05127551020408165</v>
+        <v>0.05153061224489798</v>
       </c>
     </row>
     <row r="8">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.878 (0.841–0.915)</t>
+          <t>0.878 (0.839 – 0.917)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2896,20 +2896,20 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.878 (0.841–0.915)</t>
+          <t>0.878 (0.839 – 0.917)</t>
         </is>
       </c>
       <c r="AQ12">
         <v>0.878</v>
       </c>
       <c r="AR12">
-        <v>0.841</v>
+        <v>0.839</v>
       </c>
       <c r="AS12">
-        <v>0.915</v>
+        <v>0.917</v>
       </c>
       <c r="AT12">
-        <v>0.01887755102040818</v>
+        <v>0.01989795918367349</v>
       </c>
     </row>
     <row r="13">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>Harrell's C-index</t>
         </is>
       </c>
       <c r="V13">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Under-estimation of risk before recalibration (calibration slope &lt;1; CVD+ CS 0.69, CIL -0.25 - described as near-perfect for CVD+). Near-perfect calibration after simple recalibration (CS 0.96-1.04)</t>
+          <t>Over-estimation of risk before recalibration (calibration slope &lt;1; CVD+ CS 0.69, CIL -0.25 - described as near-perfect for CVD+). Near-perfect calibration after simple recalibration (CS 0.96-1.04)</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Harrell's C-index</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="V17">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>Harrell's C-index</t>
         </is>
       </c>
       <c r="V18">
